--- a/Result/checksun_type/AI電力基建.xlsx
+++ b/Result/checksun_type/AI電力基建.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1893,11 +1893,15 @@
           <t>111.8</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>120</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>134.45</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>134.45</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2650,7 +2654,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2665,7 +2669,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -2680,7 +2684,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2875,11 +2879,15 @@
           <t>113.85</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>121.42</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>135.67</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>121.42</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>135.67</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3632,7 +3640,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3647,7 +3655,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -3662,7 +3670,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3857,11 +3865,15 @@
           <t>115.95</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>122.92</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>136.86</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>122.92</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>136.86</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4614,7 +4626,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -4629,7 +4641,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -4644,7 +4656,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4839,11 +4851,15 @@
           <t>117.9</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>124.18</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>137.96</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>124.18</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>137.96</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5596,7 +5612,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -5611,7 +5627,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -5626,7 +5642,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5821,11 +5837,15 @@
           <t>120.6</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>125.78</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>138.98</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>125.78</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>138.98</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6578,7 +6598,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -6593,7 +6613,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -6608,7 +6628,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6803,11 +6823,15 @@
           <t>122.85</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>127.12</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>139.96</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>127.12</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>139.96</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7560,7 +7584,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7575,7 +7599,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -7590,7 +7614,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7785,11 +7809,15 @@
           <t>125.0</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>128.3</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>140.99</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>128.3</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>140.99</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8542,7 +8570,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -8557,7 +8585,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
@@ -8567,12 +8595,12 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8767,11 +8795,15 @@
           <t>125.9</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>129</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>141.56</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>141.56</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9524,7 +9556,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -9539,7 +9571,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -9549,12 +9581,12 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9749,11 +9781,15 @@
           <t>126.65</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>129.93</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>142.27</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>129.93</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>142.27</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10506,7 +10542,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -10521,22 +10557,22 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10731,11 +10767,15 @@
           <t>702.0</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>710.85</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>709.4400000000001</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>710.85</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>709.44</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -11488,7 +11528,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -11503,22 +11543,22 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -11713,11 +11753,15 @@
           <t>703.4</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>713.3</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>709.7</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>713.3</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>709.7</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -12470,7 +12514,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -12485,22 +12529,22 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -12695,11 +12739,15 @@
           <t>704.0</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>716.95</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>709.78</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>716.95</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>709.78</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -13452,7 +13500,7 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -13467,22 +13515,22 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -13677,11 +13725,15 @@
           <t>704.4</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>718.75</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>709.28</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>718.75</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>709.28</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -14434,7 +14486,7 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
@@ -14449,22 +14501,22 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -14659,11 +14711,15 @@
           <t>706.8</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>722.1</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>708.62</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>722.1</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>708.62</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -15416,7 +15472,7 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -15431,22 +15487,22 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -15641,11 +15697,15 @@
           <t>708.7</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>725.65</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>708.46</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>725.65</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>708.46</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -16398,7 +16458,7 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -16413,22 +16473,22 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -16623,11 +16683,15 @@
           <t>711.8</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>726.3</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>708.5599999999999</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>726.3</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>708.56</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -17380,7 +17444,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -17395,22 +17459,22 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -17605,11 +17669,15 @@
           <t>713.4</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>726.55</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>708.16</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>726.55</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>708.16</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18352,47 +18420,47 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -18587,11 +18655,15 @@
           <t>715.5</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>726.25</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>708.34</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>726.25</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>708.34</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
@@ -19334,7 +19406,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -19344,7 +19416,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -19354,27 +19426,27 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -19569,11 +19641,15 @@
           <t>102.3</t>
         </is>
       </c>
-      <c r="CQ20" t="n">
-        <v>101.77</v>
-      </c>
-      <c r="CR20" t="n">
-        <v>101.63</v>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>101.77</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>101.63</t>
+        </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
@@ -20311,12 +20387,12 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -20326,37 +20402,37 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
+      <c r="AY21" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -20551,11 +20627,15 @@
           <t>102.03</t>
         </is>
       </c>
-      <c r="CQ21" t="n">
-        <v>101.8</v>
-      </c>
-      <c r="CR21" t="n">
-        <v>101.75</v>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>101.8</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>101.75</t>
+        </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
@@ -21293,12 +21373,12 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -21308,37 +21388,37 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AY22" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
@@ -21533,11 +21613,15 @@
           <t>101.79</t>
         </is>
       </c>
-      <c r="CQ22" t="n">
-        <v>101.87</v>
-      </c>
-      <c r="CR22" t="n">
-        <v>101.86</v>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>101.87</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>101.86</t>
+        </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
@@ -22270,17 +22354,17 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -22290,37 +22374,37 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW23" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AY23" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
@@ -22515,11 +22599,15 @@
           <t>101.54</t>
         </is>
       </c>
-      <c r="CQ23" t="n">
-        <v>101.84</v>
-      </c>
-      <c r="CR23" t="n">
-        <v>101.89</v>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>101.84</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>101.89</t>
+        </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
@@ -23252,57 +23340,57 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW24" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
+      <c r="AY24" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
@@ -23497,11 +23585,15 @@
           <t>101.39</t>
         </is>
       </c>
-      <c r="CQ24" t="n">
-        <v>102</v>
-      </c>
-      <c r="CR24" t="n">
-        <v>101.9</v>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>101.9</t>
+        </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
@@ -24229,22 +24321,22 @@
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -24254,37 +24346,37 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW25" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AY25" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
@@ -24479,11 +24571,15 @@
           <t>101.39</t>
         </is>
       </c>
-      <c r="CQ25" t="n">
-        <v>102.14</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>101.99</v>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>102.14</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>101.99</t>
+        </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
@@ -25236,7 +25332,7 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
@@ -25251,22 +25347,22 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
@@ -25461,11 +25557,15 @@
           <t>101.24</t>
         </is>
       </c>
-      <c r="CQ26" t="n">
-        <v>102</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>102.1</v>
+      <c r="CQ26" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>102.1</t>
+        </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
@@ -26218,7 +26318,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -26233,22 +26333,22 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
@@ -26443,11 +26543,15 @@
           <t>101.24</t>
         </is>
       </c>
-      <c r="CQ27" t="n">
-        <v>101.92</v>
-      </c>
-      <c r="CR27" t="n">
-        <v>102.25</v>
+      <c r="CQ27" t="inlineStr">
+        <is>
+          <t>101.92</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>102.25</t>
+        </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
@@ -27200,7 +27304,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -27215,22 +27319,22 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
@@ -27425,11 +27529,15 @@
           <t>101.24</t>
         </is>
       </c>
-      <c r="CQ28" t="n">
-        <v>101.87</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>102.61</v>
+      <c r="CQ28" t="inlineStr">
+        <is>
+          <t>101.87</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>102.61</t>
+        </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
@@ -28182,22 +28290,22 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
@@ -28207,12 +28315,12 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -28407,11 +28515,15 @@
           <t>166.5</t>
         </is>
       </c>
-      <c r="CQ29" t="n">
-        <v>165.52</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>163.45</v>
+      <c r="CQ29" t="inlineStr">
+        <is>
+          <t>165.52</t>
+        </is>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>163.45</t>
+        </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
@@ -29164,22 +29276,22 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
@@ -29189,12 +29301,12 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
@@ -29389,11 +29501,15 @@
           <t>166.0</t>
         </is>
       </c>
-      <c r="CQ30" t="n">
-        <v>165.4</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>163.35</v>
+      <c r="CQ30" t="inlineStr">
+        <is>
+          <t>165.4</t>
+        </is>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>163.35</t>
+        </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
@@ -30146,37 +30262,37 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
@@ -30371,11 +30487,15 @@
           <t>165.55</t>
         </is>
       </c>
-      <c r="CQ31" t="n">
-        <v>165.38</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>163.27</v>
+      <c r="CQ31" t="inlineStr">
+        <is>
+          <t>165.38</t>
+        </is>
+      </c>
+      <c r="CR31" t="inlineStr">
+        <is>
+          <t>163.27</t>
+        </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
@@ -31128,7 +31248,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -31143,22 +31263,22 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -31353,11 +31473,15 @@
           <t>165.1</t>
         </is>
       </c>
-      <c r="CQ32" t="n">
-        <v>165.18</v>
-      </c>
-      <c r="CR32" t="n">
-        <v>163.06</v>
+      <c r="CQ32" t="inlineStr">
+        <is>
+          <t>165.18</t>
+        </is>
+      </c>
+      <c r="CR32" t="inlineStr">
+        <is>
+          <t>163.06</t>
+        </is>
       </c>
       <c r="CS32" t="inlineStr">
         <is>
@@ -32110,7 +32234,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
@@ -32125,22 +32249,22 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -32335,11 +32459,15 @@
           <t>164.9</t>
         </is>
       </c>
-      <c r="CQ33" t="n">
-        <v>165.22</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>162.89</v>
+      <c r="CQ33" t="inlineStr">
+        <is>
+          <t>165.22</t>
+        </is>
+      </c>
+      <c r="CR33" t="inlineStr">
+        <is>
+          <t>162.89</t>
+        </is>
       </c>
       <c r="CS33" t="inlineStr">
         <is>
@@ -33092,7 +33220,7 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
@@ -33107,22 +33235,22 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
@@ -33317,11 +33445,15 @@
           <t>164.85</t>
         </is>
       </c>
-      <c r="CQ34" t="n">
-        <v>165.45</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>162.91</v>
+      <c r="CQ34" t="inlineStr">
+        <is>
+          <t>165.45</t>
+        </is>
+      </c>
+      <c r="CR34" t="inlineStr">
+        <is>
+          <t>162.91</t>
+        </is>
       </c>
       <c r="CS34" t="inlineStr">
         <is>
@@ -34074,7 +34206,7 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
@@ -34089,22 +34221,22 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
@@ -34299,11 +34431,15 @@
           <t>165.0</t>
         </is>
       </c>
-      <c r="CQ35" t="n">
-        <v>165.48</v>
-      </c>
-      <c r="CR35" t="n">
-        <v>163.02</v>
+      <c r="CQ35" t="inlineStr">
+        <is>
+          <t>165.48</t>
+        </is>
+      </c>
+      <c r="CR35" t="inlineStr">
+        <is>
+          <t>163.02</t>
+        </is>
       </c>
       <c r="CS35" t="inlineStr">
         <is>
@@ -35056,7 +35192,7 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
@@ -35071,22 +35207,22 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
@@ -35281,11 +35417,15 @@
           <t>164.9</t>
         </is>
       </c>
-      <c r="CQ36" t="n">
-        <v>165.45</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>162.98</v>
+      <c r="CQ36" t="inlineStr">
+        <is>
+          <t>165.45</t>
+        </is>
+      </c>
+      <c r="CR36" t="inlineStr">
+        <is>
+          <t>162.98</t>
+        </is>
       </c>
       <c r="CS36" t="inlineStr">
         <is>
@@ -36028,7 +36168,7 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
@@ -36038,7 +36178,7 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
@@ -36048,27 +36188,27 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
@@ -36263,11 +36403,15 @@
           <t>164.95</t>
         </is>
       </c>
-      <c r="CQ37" t="n">
-        <v>165.32</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>163.01</v>
+      <c r="CQ37" t="inlineStr">
+        <is>
+          <t>165.32</t>
+        </is>
+      </c>
+      <c r="CR37" t="inlineStr">
+        <is>
+          <t>163.01</t>
+        </is>
       </c>
       <c r="CS37" t="inlineStr">
         <is>
@@ -37020,7 +37164,7 @@
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
@@ -37035,7 +37179,7 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
@@ -37045,12 +37189,12 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
@@ -37245,11 +37389,15 @@
           <t>69.16</t>
         </is>
       </c>
-      <c r="CQ38" t="n">
-        <v>69.87</v>
-      </c>
-      <c r="CR38" t="n">
-        <v>69.19</v>
+      <c r="CQ38" t="inlineStr">
+        <is>
+          <t>69.87</t>
+        </is>
+      </c>
+      <c r="CR38" t="inlineStr">
+        <is>
+          <t>69.19</t>
+        </is>
       </c>
       <c r="CS38" t="inlineStr">
         <is>
@@ -38002,7 +38150,7 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
@@ -38017,22 +38165,22 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
@@ -38227,11 +38375,15 @@
           <t>69.21000000000001</t>
         </is>
       </c>
-      <c r="CQ39" t="n">
-        <v>70.02</v>
-      </c>
-      <c r="CR39" t="n">
-        <v>69.16</v>
+      <c r="CQ39" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="CR39" t="inlineStr">
+        <is>
+          <t>69.16</t>
+        </is>
       </c>
       <c r="CS39" t="inlineStr">
         <is>
@@ -38984,7 +39136,7 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
@@ -38999,22 +39151,22 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
@@ -39209,11 +39361,15 @@
           <t>69.2</t>
         </is>
       </c>
-      <c r="CQ40" t="n">
-        <v>70.23999999999999</v>
-      </c>
-      <c r="CR40" t="n">
-        <v>69.12</v>
+      <c r="CQ40" t="inlineStr">
+        <is>
+          <t>70.24</t>
+        </is>
+      </c>
+      <c r="CR40" t="inlineStr">
+        <is>
+          <t>69.12</t>
+        </is>
       </c>
       <c r="CS40" t="inlineStr">
         <is>
@@ -39966,7 +40122,7 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
@@ -39981,22 +40137,22 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
@@ -40191,11 +40347,15 @@
           <t>69.32</t>
         </is>
       </c>
-      <c r="CQ41" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="CR41" t="n">
-        <v>69.06999999999999</v>
+      <c r="CQ41" t="inlineStr">
+        <is>
+          <t>70.4</t>
+        </is>
+      </c>
+      <c r="CR41" t="inlineStr">
+        <is>
+          <t>69.07</t>
+        </is>
       </c>
       <c r="CS41" t="inlineStr">
         <is>
@@ -40948,7 +41108,7 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
@@ -40963,22 +41123,22 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
@@ -41173,11 +41333,15 @@
           <t>69.41999999999999</t>
         </is>
       </c>
-      <c r="CQ42" t="n">
-        <v>70.61</v>
-      </c>
-      <c r="CR42" t="n">
-        <v>69.03</v>
+      <c r="CQ42" t="inlineStr">
+        <is>
+          <t>70.61</t>
+        </is>
+      </c>
+      <c r="CR42" t="inlineStr">
+        <is>
+          <t>69.03</t>
+        </is>
       </c>
       <c r="CS42" t="inlineStr">
         <is>
@@ -41930,7 +42094,7 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
@@ -41945,22 +42109,22 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
@@ -42155,11 +42319,15 @@
           <t>69.63</t>
         </is>
       </c>
-      <c r="CQ43" t="n">
-        <v>70.86</v>
-      </c>
-      <c r="CR43" t="n">
-        <v>69.06</v>
+      <c r="CQ43" t="inlineStr">
+        <is>
+          <t>70.86</t>
+        </is>
+      </c>
+      <c r="CR43" t="inlineStr">
+        <is>
+          <t>69.06</t>
+        </is>
       </c>
       <c r="CS43" t="inlineStr">
         <is>
@@ -42912,7 +43080,7 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
@@ -42927,22 +43095,22 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
@@ -43137,11 +43305,15 @@
           <t>69.85999999999999</t>
         </is>
       </c>
-      <c r="CQ44" t="n">
-        <v>70.98999999999999</v>
-      </c>
-      <c r="CR44" t="n">
-        <v>69.06999999999999</v>
+      <c r="CQ44" t="inlineStr">
+        <is>
+          <t>70.99</t>
+        </is>
+      </c>
+      <c r="CR44" t="inlineStr">
+        <is>
+          <t>69.07</t>
+        </is>
       </c>
       <c r="CS44" t="inlineStr">
         <is>
@@ -43894,7 +44066,7 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
@@ -43909,22 +44081,22 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
@@ -44119,11 +44291,15 @@
           <t>70.03999999999999</t>
         </is>
       </c>
-      <c r="CQ45" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="CR45" t="n">
-        <v>68.97</v>
+      <c r="CQ45" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
+      <c r="CR45" t="inlineStr">
+        <is>
+          <t>68.97</t>
+        </is>
       </c>
       <c r="CS45" t="inlineStr">
         <is>
@@ -44876,7 +45052,7 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
@@ -44891,22 +45067,22 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
@@ -45101,11 +45277,15 @@
           <t>70.3</t>
         </is>
       </c>
-      <c r="CQ46" t="n">
-        <v>71.22</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>68.92</v>
+      <c r="CQ46" t="inlineStr">
+        <is>
+          <t>71.22</t>
+        </is>
+      </c>
+      <c r="CR46" t="inlineStr">
+        <is>
+          <t>68.92</t>
+        </is>
       </c>
       <c r="CS46" t="inlineStr">
         <is>
@@ -45858,7 +46038,7 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
@@ -45873,22 +46053,22 @@
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
@@ -46083,11 +46263,15 @@
           <t>197.1</t>
         </is>
       </c>
-      <c r="CQ47" t="n">
-        <v>199.6</v>
-      </c>
-      <c r="CR47" t="n">
-        <v>199.44</v>
+      <c r="CQ47" t="inlineStr">
+        <is>
+          <t>199.6</t>
+        </is>
+      </c>
+      <c r="CR47" t="inlineStr">
+        <is>
+          <t>199.44</t>
+        </is>
       </c>
       <c r="CS47" t="inlineStr">
         <is>
@@ -46840,7 +47024,7 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
@@ -46855,22 +47039,22 @@
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
@@ -47065,11 +47249,15 @@
           <t>196.95</t>
         </is>
       </c>
-      <c r="CQ48" t="n">
-        <v>200.05</v>
-      </c>
-      <c r="CR48" t="n">
-        <v>199.73</v>
+      <c r="CQ48" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="CR48" t="inlineStr">
+        <is>
+          <t>199.73</t>
+        </is>
       </c>
       <c r="CS48" t="inlineStr">
         <is>
@@ -47822,7 +48010,7 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
@@ -47837,22 +48025,22 @@
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
@@ -48047,11 +48235,15 @@
           <t>196.7</t>
         </is>
       </c>
-      <c r="CQ49" t="n">
-        <v>200.6</v>
-      </c>
-      <c r="CR49" t="n">
-        <v>199.93</v>
+      <c r="CQ49" t="inlineStr">
+        <is>
+          <t>200.6</t>
+        </is>
+      </c>
+      <c r="CR49" t="inlineStr">
+        <is>
+          <t>199.93</t>
+        </is>
       </c>
       <c r="CS49" t="inlineStr">
         <is>
@@ -48804,7 +48996,7 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
@@ -48819,22 +49011,22 @@
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
@@ -49029,11 +49221,15 @@
           <t>196.65</t>
         </is>
       </c>
-      <c r="CQ50" t="n">
-        <v>200.72</v>
-      </c>
-      <c r="CR50" t="n">
-        <v>199.98</v>
+      <c r="CQ50" t="inlineStr">
+        <is>
+          <t>200.72</t>
+        </is>
+      </c>
+      <c r="CR50" t="inlineStr">
+        <is>
+          <t>199.98</t>
+        </is>
       </c>
       <c r="CS50" t="inlineStr">
         <is>
@@ -49786,7 +49982,7 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
@@ -49801,22 +49997,22 @@
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
@@ -50011,11 +50207,15 @@
           <t>197.45</t>
         </is>
       </c>
-      <c r="CQ51" t="n">
-        <v>201.3</v>
-      </c>
-      <c r="CR51" t="n">
-        <v>199.98</v>
+      <c r="CQ51" t="inlineStr">
+        <is>
+          <t>201.3</t>
+        </is>
+      </c>
+      <c r="CR51" t="inlineStr">
+        <is>
+          <t>199.98</t>
+        </is>
       </c>
       <c r="CS51" t="inlineStr">
         <is>
@@ -50768,7 +50968,7 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
@@ -50783,22 +50983,22 @@
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
@@ -50993,11 +51193,15 @@
           <t>198.35</t>
         </is>
       </c>
-      <c r="CQ52" t="n">
-        <v>202.12</v>
-      </c>
-      <c r="CR52" t="n">
-        <v>200.14</v>
+      <c r="CQ52" t="inlineStr">
+        <is>
+          <t>202.12</t>
+        </is>
+      </c>
+      <c r="CR52" t="inlineStr">
+        <is>
+          <t>200.14</t>
+        </is>
       </c>
       <c r="CS52" t="inlineStr">
         <is>
@@ -51750,7 +51954,7 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
@@ -51765,22 +51969,22 @@
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
@@ -51975,11 +52179,15 @@
           <t>199.3</t>
         </is>
       </c>
-      <c r="CQ53" t="n">
-        <v>202.4</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>200.4</v>
+      <c r="CQ53" t="inlineStr">
+        <is>
+          <t>202.4</t>
+        </is>
+      </c>
+      <c r="CR53" t="inlineStr">
+        <is>
+          <t>200.4</t>
+        </is>
       </c>
       <c r="CS53" t="inlineStr">
         <is>
@@ -52732,7 +52940,7 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
@@ -52747,22 +52955,22 @@
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
@@ -52957,11 +53165,15 @@
           <t>200.05</t>
         </is>
       </c>
-      <c r="CQ54" t="n">
-        <v>202.52</v>
-      </c>
-      <c r="CR54" t="n">
-        <v>200.56</v>
+      <c r="CQ54" t="inlineStr">
+        <is>
+          <t>202.52</t>
+        </is>
+      </c>
+      <c r="CR54" t="inlineStr">
+        <is>
+          <t>200.56</t>
+        </is>
       </c>
       <c r="CS54" t="inlineStr">
         <is>
@@ -53714,7 +53926,7 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
@@ -53724,27 +53936,27 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
@@ -53939,11 +54151,15 @@
           <t>200.95</t>
         </is>
       </c>
-      <c r="CQ55" t="n">
-        <v>202.58</v>
-      </c>
-      <c r="CR55" t="n">
-        <v>200.99</v>
+      <c r="CQ55" t="inlineStr">
+        <is>
+          <t>202.58</t>
+        </is>
+      </c>
+      <c r="CR55" t="inlineStr">
+        <is>
+          <t>200.99</t>
+        </is>
       </c>
       <c r="CS55" t="inlineStr">
         <is>
